--- a/static/demo/downloads/kpi-scorecard.xlsx
+++ b/static/demo/downloads/kpi-scorecard.xlsx
@@ -7,9 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Board KPIs" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPI Scorecard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'KPI Scorecard'!$A$2:$G$16</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,28 +29,53 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="001B2A4A"/>
       <sz val="14"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00333333"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00333333"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001B2A4A"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -57,8 +85,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F5F5F5"/>
-        <bgColor rgb="00F5F5F5"/>
+        <fgColor rgb="00FAFAFA"/>
+        <bgColor rgb="00FAFAFA"/>
       </patternFill>
     </fill>
   </fills>
@@ -88,22 +116,96 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="002C5F2D"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00E8F5E9"/>
+          <bgColor rgb="00E8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00D4A843"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFF8E1"/>
+          <bgColor rgb="00FFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00B85042"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFEBEE"/>
+          <bgColor rgb="00FFEBEE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -466,315 +568,766 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="35" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Board KPI Scorecard — Meridian Healthcare Q2 2026</t>
+          <t>CDAIO KPI Scorecard - Q1 2026</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>KPI</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Current Value</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Trend</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>KPI</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Current</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Target (12mo)</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Healthcare Avg</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Trend</t>
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Value Delivery</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>AI Value Delivered ($)</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>$2.4M</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>$2.0M</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>+18% QoQ</t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>Finance team</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Overall AI Maturity</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>2.2/5.0</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>3.5/5.0</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>2.8/5.0</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Behind</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="A4" s="10" t="inlineStr"/>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Use Cases in Production</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>+3 this quarter</t>
+        </is>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>AI/ML platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr"/>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>ROI on AI Investment</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>4.5x</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>3.0x</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>+0.8x QoQ</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>Finance team</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>Operational Excellence</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Model Adoption Rate</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>+5% QoQ</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>Usage analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Platform Uptime</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>98.2%</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>99.0%</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>Amber</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>-0.3% QoQ</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>SRE dashboard</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr"/>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Models in Production</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>+23 new</t>
+        </is>
+      </c>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>MLOps platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Data Quality Score</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>87%</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>+4% QoQ</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>DQ monitoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr"/>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Critical Data Issues</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>-3 from last Q</t>
+        </is>
+      </c>
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>Jira tracker</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Data Catalog Coverage</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>Amber</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>+8% QoQ</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>Data catalog</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Policy Compliance Rate</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>78%</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>Amber</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>+12% QoQ</t>
+        </is>
+      </c>
+      <c r="G12" s="14" t="inlineStr">
+        <is>
+          <t>GRC platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr"/>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Data Steward Coverage</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>+15% QoQ</t>
+        </is>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>Governance office</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr"/>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>Regulatory Gaps Open</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>-1 from last Q</t>
+        </is>
+      </c>
+      <c r="G14" s="14" t="inlineStr">
+        <is>
+          <t>Compliance tracker</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Stakeholder</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Stakeholder NPS</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>Amber</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>-0.3 QoQ</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>Quarterly survey</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr"/>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>Self-Service Adoption</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>Amber</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>+5% QoQ</t>
+        </is>
+      </c>
+      <c r="G16" s="14" t="inlineStr">
+        <is>
+          <t>Analytics platform</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:G16"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="E3:E16">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>E3="Green"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1">
+      <formula>E3="Amber"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="2">
+      <formula>E3="Red"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="002D4A7A"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="35" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>KPI Status by Category</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Total KPIs</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Amber</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Value Delivery</t>
+        </is>
+      </c>
+      <c r="B3" s="7">
+        <f>COUNTIF('KPI Scorecard'!A$3:A$16,A3)</f>
+        <v/>
+      </c>
+      <c r="C3" s="7">
+        <f>COUNTIFS('KPI Scorecard'!A$3:A$16,A3,'KPI Scorecard'!E$3:E$16,"Green")</f>
+        <v/>
+      </c>
+      <c r="D3" s="7">
+        <f>COUNTIFS('KPI Scorecard'!A$3:A$16,A3,'KPI Scorecard'!E$3:E$16,"Amber")</f>
+        <v/>
+      </c>
+      <c r="E3" s="7">
+        <f>COUNTIFS('KPI Scorecard'!A$3:A$16,A3,'KPI Scorecard'!E$3:E$16,"Red")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>Operational Excellence</t>
+        </is>
+      </c>
+      <c r="B4" s="12">
+        <f>COUNTIF('KPI Scorecard'!A$3:A$16,A4)</f>
+        <v/>
+      </c>
+      <c r="C4" s="12">
+        <f>COUNTIFS('KPI Scorecard'!A$3:A$16,A4,'KPI Scorecard'!E$3:E$16,"Green")</f>
+        <v/>
+      </c>
+      <c r="D4" s="12">
+        <f>COUNTIFS('KPI Scorecard'!A$3:A$16,A4,'KPI Scorecard'!E$3:E$16,"Amber")</f>
+        <v/>
+      </c>
+      <c r="E4" s="12">
+        <f>COUNTIFS('KPI Scorecard'!A$3:A$16,A4,'KPI Scorecard'!E$3:E$16,"Red")</f>
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>AI Spend / Revenue</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>0.03%</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="B5" s="7">
+        <f>COUNTIF('KPI Scorecard'!A$3:A$16,A5)</f>
+        <v/>
+      </c>
+      <c r="C5" s="7">
+        <f>COUNTIFS('KPI Scorecard'!A$3:A$16,A5,'KPI Scorecard'!E$3:E$16,"Green")</f>
+        <v/>
+      </c>
+      <c r="D5" s="7">
+        <f>COUNTIFS('KPI Scorecard'!A$3:A$16,A5,'KPI Scorecard'!E$3:E$16,"Amber")</f>
+        <v/>
+      </c>
+      <c r="E5" s="7">
+        <f>COUNTIFS('KPI Scorecard'!A$3:A$16,A5,'KPI Scorecard'!E$3:E$16,"Red")</f>
+        <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Models in Production</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>Behind</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="B6" s="12">
+        <f>COUNTIF('KPI Scorecard'!A$3:A$16,A6)</f>
+        <v/>
+      </c>
+      <c r="C6" s="12">
+        <f>COUNTIFS('KPI Scorecard'!A$3:A$16,A6,'KPI Scorecard'!E$3:E$16,"Green")</f>
+        <v/>
+      </c>
+      <c r="D6" s="12">
+        <f>COUNTIFS('KPI Scorecard'!A$3:A$16,A6,'KPI Scorecard'!E$3:E$16,"Amber")</f>
+        <v/>
+      </c>
+      <c r="E6" s="12">
+        <f>COUNTIFS('KPI Scorecard'!A$3:A$16,A6,'KPI Scorecard'!E$3:E$16,"Red")</f>
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Data Quality Score</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>62%</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>85%</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>75%</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>Below Avg</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Stakeholder</t>
+        </is>
+      </c>
+      <c r="B7" s="7">
+        <f>COUNTIF('KPI Scorecard'!A$3:A$16,A7)</f>
+        <v/>
+      </c>
+      <c r="C7" s="7">
+        <f>COUNTIFS('KPI Scorecard'!A$3:A$16,A7,'KPI Scorecard'!E$3:E$16,"Green")</f>
+        <v/>
+      </c>
+      <c r="D7" s="7">
+        <f>COUNTIFS('KPI Scorecard'!A$3:A$16,A7,'KPI Scorecard'!E$3:E$16,"Amber")</f>
+        <v/>
+      </c>
+      <c r="E7" s="7">
+        <f>COUNTIFS('KPI Scorecard'!A$3:A$16,A7,'KPI Scorecard'!E$3:E$16,"Red")</f>
+        <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Governance Maturity</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>1.6/5.0</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>3.5/5.0</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>2.4/5.0</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>POC-to-Prod Cycle</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>8 months</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>8 weeks</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>4 months</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>Behind</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Data Team Size</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>Below Avg</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Annual AI ROI</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>$2.8M</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>$1.5M</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>SUM(B3:B7)</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>SUM(C3:C7)</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>SUM(D3:D7)</f>
+        <v/>
+      </c>
+      <c r="E8" s="3">
+        <f>SUM(E3:E7)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
